--- a/output/processing/114-115_740.xlsx
+++ b/output/processing/114-115_740.xlsx
@@ -531,28 +531,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="33" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="47" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -653,9 +653,141 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>mediO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>220-240V~ 50/60 Hz</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>350 W</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>18 Nm (*)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10 Kg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>295 x 181 x 320 mm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>IP44</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-20°C ÷ +55°C</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>S3 - 30%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>12 m/min</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10 μF</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Magnetico</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>740D incorporata</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mediO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>(*) dati riferiti a 230V~ 50Hz.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Dispositivo di sblocco</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mediO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Manopola di sblocco rotativa - chiave cifrata</t>
         </is>
       </c>
     </row>
